--- a/Python/Modèles/Evaluation-Stagiaires-Modèle.xlsx
+++ b/Python/Modèles/Evaluation-Stagiaires-Modèle.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vt238770\Documents\_CEA\Prog\Modèles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vt238770\Documents\_CEA\Prog\Python\Modèles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1A9D94F-DB3A-4733-BA60-014DB8D816FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{671A35B0-8219-4D45-95FA-80690AA76E97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stagiaires" sheetId="1" r:id="rId1"/>
@@ -38,8 +38,13 @@
   </definedNames>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId6"/>
+    <pivotCache cacheId="2" r:id="rId6"/>
   </pivotCaches>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1006,6 +1011,173 @@
       <alignment horizontal="general" vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <border>
+        <right style="medium">
+          <color theme="9" tint="-0.24994659260841701"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <right style="medium">
+          <color theme="9" tint="-0.24994659260841701"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <right style="medium">
+          <color theme="9" tint="-0.24994659260841701"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <right style="medium">
+          <color theme="9" tint="-0.24994659260841701"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <right style="medium">
+          <color theme="9" tint="-0.24994659260841701"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <right style="medium">
+          <color theme="9" tint="-0.24994659260841701"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <right style="medium">
+          <color theme="9" tint="-0.24994659260841701"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <right style="medium">
+          <color theme="9" tint="-0.24994659260841701"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <right style="medium">
+          <color theme="9" tint="-0.24994659260841701"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <right style="medium">
+          <color theme="9" tint="-0.24994659260841701"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <right style="medium">
+          <color theme="9" tint="-0.24994659260841701"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <right style="medium">
+          <color theme="9" tint="-0.24994659260841701"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color theme="9" tint="-0.24994659260841701"/>
+        </left>
+        <right style="medium">
+          <color theme="9" tint="-0.24994659260841701"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color theme="9" tint="-0.24994659260841701"/>
+        </left>
+        <right style="medium">
+          <color theme="9" tint="-0.24994659260841701"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color theme="9" tint="-0.24994659260841701"/>
+        </left>
+        <right style="medium">
+          <color theme="9" tint="-0.24994659260841701"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color theme="9" tint="-0.24994659260841701"/>
+        </left>
+        <right style="medium">
+          <color theme="9" tint="-0.24994659260841701"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
       <border>
         <bottom style="medium">
           <color theme="9" tint="-0.24994659260841701"/>
@@ -1115,173 +1287,6 @@
           <bgColor theme="5" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="medium">
-          <color theme="9" tint="-0.24994659260841701"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="medium">
-          <color theme="9" tint="-0.24994659260841701"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="medium">
-          <color theme="9" tint="-0.24994659260841701"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="medium">
-          <color theme="9" tint="-0.24994659260841701"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="medium">
-          <color theme="9" tint="-0.24994659260841701"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="medium">
-          <color theme="9" tint="-0.24994659260841701"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="medium">
-          <color theme="9" tint="-0.24994659260841701"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="medium">
-          <color theme="9" tint="-0.24994659260841701"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="medium">
-          <color theme="9" tint="-0.24994659260841701"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="medium">
-          <color theme="9" tint="-0.24994659260841701"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="medium">
-          <color theme="9" tint="-0.24994659260841701"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="medium">
-          <color theme="9" tint="-0.24994659260841701"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color theme="9" tint="-0.24994659260841701"/>
-        </left>
-        <right style="medium">
-          <color theme="9" tint="-0.24994659260841701"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color theme="9" tint="-0.24994659260841701"/>
-        </left>
-        <right style="medium">
-          <color theme="9" tint="-0.24994659260841701"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color theme="9" tint="-0.24994659260841701"/>
-        </left>
-        <right style="medium">
-          <color theme="9" tint="-0.24994659260841701"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color theme="9" tint="-0.24994659260841701"/>
-        </left>
-        <right style="medium">
-          <color theme="9" tint="-0.24994659260841701"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
     </dxf>
     <dxf>
       <fill>
@@ -4047,281 +4052,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0100-000000000000}" name="Tableau croisé dynamique1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="7" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" rowHeaderCaption="Critères">
-  <location ref="B11:C25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="16">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="6"/>
-        <item x="9"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="10"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item h="1" x="8"/>
-        <item x="0"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="7"/>
-        <item h="1" x="11"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="13"/>
-  </rowFields>
-  <rowItems count="14">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Note moyenne" fld="14" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <formats count="15">
-    <format dxfId="44">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="13" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="43">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="13" count="4">
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="42">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="13" count="2">
-            <x v="6"/>
-            <x v="7"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="41">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="13" count="4">
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="12"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="40">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="13" count="1">
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="39">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="13" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="38">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="13" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="37">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="13" count="4">
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="36">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="13" count="4">
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="35">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="13" count="2">
-            <x v="6"/>
-            <x v="7"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="34">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="13" count="2">
-            <x v="6"/>
-            <x v="7"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="33">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="13" count="4">
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="12"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="32">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="13" count="4">
-            <x v="9"/>
-            <x v="10"/>
-            <x v="11"/>
-            <x v="12"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="31">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="13" count="1">
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="30">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="13" count="1">
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleMedium14" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0100-000001000000}" name="Tableau croisé dynamique2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="7" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" rowHeaderCaption="NOM Prénom" colHeaderCaption="Critères">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0100-000001000000}" name="Tableau croisé dynamique2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="7" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" rowHeaderCaption="NOM Prénom" colHeaderCaption="Critères">
   <location ref="B36:P49" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="16">
     <pivotField showAll="0"/>
@@ -4468,27 +4199,27 @@
     <dataField name=" " fld="14" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="25">
-    <format dxfId="69">
+    <format dxfId="54">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="13" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="68">
+    <format dxfId="53">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="67">
+    <format dxfId="52">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="13" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="66">
+    <format dxfId="51">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="65">
+    <format dxfId="50">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="13" count="2">
@@ -4498,7 +4229,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="64">
+    <format dxfId="49">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="13" count="4">
@@ -4510,7 +4241,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="63">
+    <format dxfId="48">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="13" count="2">
@@ -4520,7 +4251,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="62">
+    <format dxfId="47">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="13" count="1">
@@ -4529,7 +4260,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="61">
+    <format dxfId="46">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="13" count="2" selected="0">
@@ -4539,13 +4270,13 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="60">
+    <format dxfId="45">
       <pivotArea field="13" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="59">
+    <format dxfId="44">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" offset="A1" fieldPosition="0"/>
     </format>
-    <format dxfId="58">
+    <format dxfId="43">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="13" count="2">
@@ -4555,7 +4286,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="57">
+    <format dxfId="42">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="13" count="4" selected="0">
@@ -4567,10 +4298,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="56">
+    <format dxfId="41">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" offset="B1:E1" fieldPosition="0"/>
     </format>
-    <format dxfId="55">
+    <format dxfId="40">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="13" count="4">
@@ -4582,7 +4313,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="54">
+    <format dxfId="39">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="13" count="2" selected="0">
@@ -4592,10 +4323,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="53">
+    <format dxfId="38">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" offset="F1:G1" fieldPosition="0"/>
     </format>
-    <format dxfId="52">
+    <format dxfId="37">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="13" count="2">
@@ -4605,7 +4336,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="51">
+    <format dxfId="36">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="13" count="4" selected="0">
@@ -4617,10 +4348,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="50">
+    <format dxfId="35">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" offset="H1:K1" fieldPosition="0"/>
     </format>
-    <format dxfId="49">
+    <format dxfId="34">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="13" count="4">
@@ -4632,7 +4363,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="48">
+    <format dxfId="33">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="13" count="1" selected="0">
@@ -4641,10 +4372,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="47">
+    <format dxfId="32">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" offset="L1" fieldPosition="0"/>
     </format>
-    <format dxfId="46">
+    <format dxfId="31">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="13" count="1">
@@ -4653,8 +4384,282 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="45">
+    <format dxfId="30">
       <pivotArea field="11" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleMedium14" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0100-000000000000}" name="Tableau croisé dynamique1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="7" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" rowHeaderCaption="Critères">
+  <location ref="B11:C25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="16">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="6"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="10"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item h="1" x="8"/>
+        <item x="0"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="7"/>
+        <item h="1" x="11"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="13"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Note moyenne" fld="14" subtotal="average" baseField="1" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <formats count="15">
+    <format dxfId="69">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="13" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="68">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="13" count="4">
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="67">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="13" count="2">
+            <x v="6"/>
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="66">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="13" count="4">
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="12"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="65">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="13" count="1">
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="64">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="13" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="63">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="13" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="62">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="13" count="4">
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="61">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="13" count="4">
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="60">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="13" count="2">
+            <x v="6"/>
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="59">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="13" count="2">
+            <x v="6"/>
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="58">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="13" count="4">
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="12"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="57">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="13" count="4">
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="12"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="56">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="13" count="1">
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="55">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="13" count="1">
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
     </format>
   </formats>
   <chartFormats count="1">
